--- a/ERETTSEGI/DK/2023okt/Forras/1B_Dronreptetes/dron.xlsx
+++ b/ERETTSEGI/DK/2023okt/Forras/1B_Dronreptetes/dron.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\suliscucc\suli\ERETTSEGI\DK\2023okt\Forras\1B_Dronreptetes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C1941-6C13-4099-B801-C185ED73129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B35124F-21AD-4F98-A4F3-4627B7DED4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6DB44F85-FFC1-433C-BCD0-27C55581C495}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7D451D5-0760-4AF0-8A14-15AB0E52884B}"/>
   </bookViews>
   <sheets>
-    <sheet name="tesztrepülés" sheetId="1" r:id="rId1"/>
+    <sheet name="Tesztrepülés" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,30 +31,11 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -75,13 +56,13 @@
     <t>Égtáj</t>
   </si>
   <si>
-    <t>Égtájváltás</t>
+    <t>Égtájvátás</t>
   </si>
   <si>
     <t>Égtájak</t>
   </si>
   <si>
-    <t>Előfordulásuk Száma</t>
+    <t>Előfordulásuk száma</t>
   </si>
   <si>
     <t>É</t>
@@ -90,37 +71,29 @@
     <t>K</t>
   </si>
   <si>
+    <t>Ny</t>
+  </si>
+  <si>
     <t>D</t>
   </si>
   <si>
-    <t>Ny</t>
+    <t>Legtöbszőr ezen égtáj felé repült:</t>
   </si>
   <si>
-    <t>Legtöbbször ezen égtáj felé repült:</t>
+    <t>Legnagyobb elért magasság(cm):</t>
   </si>
   <si>
-    <t>Legnagyobb elért magasság (cm):</t>
+    <t>Égtájvátások aránya:</t>
   </si>
   <si>
-    <t>Égtájváltások aránya:</t>
-  </si>
-  <si>
-    <t>Pozitív / negatív / nulla elfordulások száma:</t>
+    <t>Pozitív/negtív/nulla előfordulások száma:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,20 +120,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
-    <cellStyle name="Százalék" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -173,6 +146,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>175714</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>257175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>391281</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>76963</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Kép 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84EEC92B-04BE-610B-2E45-851029AF3F38}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8929189" y="257175"/>
+          <a:ext cx="2653967" cy="2677288"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,20 +513,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DF6A147-57A7-4FF4-906E-B265F6E82079}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CD1E24-097C-49FF-B9A3-5DF2D5B3D66A}">
   <dimension ref="A1:K201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
     <col min="9" max="9" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -517,10 +538,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -538,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="str">
-        <f>IF(OR(D2&gt;=315,D2&lt;45),"É",IF(AND(D2&gt;=45,D2&lt;135),"K",IF(AND(D2&gt;=135,D2&lt;225),"D","Ny")))</f>
+        <f>IF(AND(D2&gt;=45,D2&lt;135),"K",IF(AND(D2&gt;=135,D2&lt;225),"D",IF(AND(D2&gt;=225,D2&lt;315),"Ny","É")))</f>
         <v>É</v>
       </c>
       <c r="H2" t="s">
@@ -563,18 +584,18 @@
         <v>4</v>
       </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E66" si="0">IF(OR(D3&gt;=315,D3&lt;45),"É",IF(AND(D3&gt;=45,D3&lt;135),"K",IF(AND(D3&gt;=135,D3&lt;225),"D","Ny")))</f>
+        <f t="shared" ref="E3:E66" si="0">IF(AND(D3&gt;=45,D3&lt;135),"K",IF(AND(D3&gt;=135,D3&lt;225),"D",IF(AND(D3&gt;=225,D3&lt;315),"Ny","É")))</f>
         <v>É</v>
       </c>
       <c r="F3" t="str">
-        <f>IF(E3=E2,"Hamis","Igaz")</f>
-        <v>Hamis</v>
+        <f>IF(E3=E2,"HAMIS","IGAZ")</f>
+        <v>HAMIS</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
       </c>
       <c r="I3">
-        <f>COUNTIF(E2:E201,H3)</f>
+        <f>COUNTIF($E$2:$E$201,H3)</f>
         <v>39</v>
       </c>
     </row>
@@ -597,14 +618,14 @@
         <v>É</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4:F67" si="2">IF(E4=E3,"Hamis","Igaz")</f>
-        <v>Hamis</v>
+        <f t="shared" ref="F4:F67" si="2">IF(E4=E3,"HAMIS","IGAZ")</f>
+        <v>HAMIS</v>
       </c>
       <c r="H4" t="s">
         <v>9</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I6" si="3">COUNTIF(E3:E202,H4)</f>
+        <f>COUNTIF($E$2:$E$201,H4)</f>
         <v>67</v>
       </c>
     </row>
@@ -628,14 +649,14 @@
       </c>
       <c r="F5" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
       <c r="H5" t="s">
         <v>10</v>
       </c>
       <c r="I5">
-        <f t="shared" si="3"/>
-        <v>57</v>
+        <f>COUNTIF($E$2:$E$201,H5)</f>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -658,14 +679,14 @@
       </c>
       <c r="F6" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
       </c>
       <c r="I6">
-        <f t="shared" si="3"/>
-        <v>37</v>
+        <f>COUNTIF($E$2:$E$201,H6)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -688,12 +709,12 @@
       </c>
       <c r="F7" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
       </c>
-      <c r="K7" t="str">
+      <c r="K7" s="2" t="str">
         <f>_xlfn.XLOOKUP(MAX(I3:I6),I3:I6,H3:H6)</f>
         <v>K</v>
       </c>
@@ -718,12 +739,12 @@
       </c>
       <c r="F8" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
       <c r="H8" t="s">
         <v>13</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <f>MAX(B2:B201)</f>
         <v>889</v>
       </c>
@@ -748,14 +769,14 @@
       </c>
       <c r="F9" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
       <c r="H9" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="K9" ca="1">_xludf.COUNTIF(F3:F201,TRUE)/COUNTA(F3:F201)</f>
-        <v>#NAME?</v>
+      <c r="K9" s="2" t="b">
+        <f>ISNUMBER(_xlfn.PERCENTOF("IGAZ",COUNTA(F3:F201)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -778,14 +799,14 @@
       </c>
       <c r="F10" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
       </c>
-      <c r="K10" t="e" cm="1">
-        <f t="array" ref="K10">DARABTELI</f>
-        <v>#NAME?</v>
+      <c r="K10" s="2" t="str">
+        <f>COUNTIF(C2:C201,"&gt;0")&amp;"/"&amp;COUNTIF(C2:C201,"&lt;0")&amp;"/"&amp;COUNTIF(C2:C201,"=0")</f>
+        <v>128/58/14</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -808,7 +829,7 @@
       </c>
       <c r="F11" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -831,7 +852,7 @@
       </c>
       <c r="F12" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -854,7 +875,7 @@
       </c>
       <c r="F13" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -877,7 +898,7 @@
       </c>
       <c r="F14" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -900,7 +921,7 @@
       </c>
       <c r="F15" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -923,7 +944,7 @@
       </c>
       <c r="F16" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -946,7 +967,7 @@
       </c>
       <c r="F17" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -969,7 +990,7 @@
       </c>
       <c r="F18" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -992,7 +1013,7 @@
       </c>
       <c r="F19" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1015,7 +1036,7 @@
       </c>
       <c r="F20" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1038,7 +1059,7 @@
       </c>
       <c r="F21" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1061,7 +1082,7 @@
       </c>
       <c r="F22" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1084,7 +1105,7 @@
       </c>
       <c r="F23" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1107,7 +1128,7 @@
       </c>
       <c r="F24" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1130,7 +1151,7 @@
       </c>
       <c r="F25" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1153,7 +1174,7 @@
       </c>
       <c r="F26" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1176,7 +1197,7 @@
       </c>
       <c r="F27" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,7 +1220,7 @@
       </c>
       <c r="F28" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1222,7 +1243,7 @@
       </c>
       <c r="F29" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1245,7 +1266,7 @@
       </c>
       <c r="F30" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1268,7 +1289,7 @@
       </c>
       <c r="F31" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1291,7 +1312,7 @@
       </c>
       <c r="F32" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1314,7 +1335,7 @@
       </c>
       <c r="F33" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1337,7 +1358,7 @@
       </c>
       <c r="F34" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1360,7 +1381,7 @@
       </c>
       <c r="F35" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1383,7 +1404,7 @@
       </c>
       <c r="F36" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1406,7 +1427,7 @@
       </c>
       <c r="F37" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1429,7 +1450,7 @@
       </c>
       <c r="F38" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1452,7 +1473,7 @@
       </c>
       <c r="F39" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1475,7 +1496,7 @@
       </c>
       <c r="F40" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,7 +1519,7 @@
       </c>
       <c r="F41" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,7 +1542,7 @@
       </c>
       <c r="F42" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,7 +1565,7 @@
       </c>
       <c r="F43" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1567,7 +1588,7 @@
       </c>
       <c r="F44" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1590,7 +1611,7 @@
       </c>
       <c r="F45" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1613,7 +1634,7 @@
       </c>
       <c r="F46" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1636,7 +1657,7 @@
       </c>
       <c r="F47" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1659,7 +1680,7 @@
       </c>
       <c r="F48" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1682,7 +1703,7 @@
       </c>
       <c r="F49" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1705,7 +1726,7 @@
       </c>
       <c r="F50" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1728,7 +1749,7 @@
       </c>
       <c r="F51" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1751,7 +1772,7 @@
       </c>
       <c r="F52" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1774,7 +1795,7 @@
       </c>
       <c r="F53" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1797,7 +1818,7 @@
       </c>
       <c r="F54" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1820,7 +1841,7 @@
       </c>
       <c r="F55" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,7 +1864,7 @@
       </c>
       <c r="F56" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1866,7 +1887,7 @@
       </c>
       <c r="F57" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1889,7 +1910,7 @@
       </c>
       <c r="F58" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1912,7 +1933,7 @@
       </c>
       <c r="F59" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1935,7 +1956,7 @@
       </c>
       <c r="F60" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,7 +1979,7 @@
       </c>
       <c r="F61" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1981,7 +2002,7 @@
       </c>
       <c r="F62" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2004,7 +2025,7 @@
       </c>
       <c r="F63" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2027,7 +2048,7 @@
       </c>
       <c r="F64" t="str">
         <f t="shared" si="2"/>
-        <v>Igaz</v>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2050,7 +2071,7 @@
       </c>
       <c r="F65" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2073,7 +2094,7 @@
       </c>
       <c r="F66" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2091,12 +2112,12 @@
         <v>94</v>
       </c>
       <c r="E67" t="str">
-        <f t="shared" ref="E67:E130" si="4">IF(OR(D67&gt;=315,D67&lt;45),"É",IF(AND(D67&gt;=45,D67&lt;135),"K",IF(AND(D67&gt;=135,D67&lt;225),"D","Ny")))</f>
+        <f t="shared" ref="E67:E130" si="3">IF(AND(D67&gt;=45,D67&lt;135),"K",IF(AND(D67&gt;=135,D67&lt;225),"D",IF(AND(D67&gt;=225,D67&lt;315),"Ny","É")))</f>
         <v>K</v>
       </c>
       <c r="F67" t="str">
         <f t="shared" si="2"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2110,16 +2131,16 @@
         <v>20</v>
       </c>
       <c r="D68">
-        <f t="shared" ref="D68:D131" si="5">MOD(D67+C68,360)</f>
+        <f t="shared" ref="D68:D131" si="4">MOD(D67+C68,360)</f>
         <v>114</v>
       </c>
       <c r="E68" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" ref="F68:F131" si="6">IF(E68=E67,"Hamis","Igaz")</f>
-        <v>Hamis</v>
+        <f t="shared" ref="F68:F131" si="5">IF(E68=E67,"HAMIS","IGAZ")</f>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2133,16 +2154,16 @@
         <v>8</v>
       </c>
       <c r="D69">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>122</v>
       </c>
       <c r="E69" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2156,16 +2177,16 @@
         <v>5</v>
       </c>
       <c r="D70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>127</v>
       </c>
       <c r="E70" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2179,16 +2200,16 @@
         <v>-16</v>
       </c>
       <c r="D71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>111</v>
       </c>
       <c r="E71" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2202,16 +2223,16 @@
         <v>15</v>
       </c>
       <c r="D72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>126</v>
       </c>
       <c r="E72" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2225,16 +2246,16 @@
         <v>-1</v>
       </c>
       <c r="D73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>125</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2248,16 +2269,16 @@
         <v>-20</v>
       </c>
       <c r="D74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>105</v>
       </c>
       <c r="E74" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2271,16 +2292,16 @@
         <v>1</v>
       </c>
       <c r="D75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>106</v>
       </c>
       <c r="E75" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2294,16 +2315,16 @@
         <v>-14</v>
       </c>
       <c r="D76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="E76" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2317,16 +2338,16 @@
         <v>-8</v>
       </c>
       <c r="D77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>84</v>
       </c>
       <c r="E77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2340,16 +2361,16 @@
         <v>11</v>
       </c>
       <c r="D78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>95</v>
       </c>
       <c r="E78" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F78" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,16 +2384,16 @@
         <v>-19</v>
       </c>
       <c r="D79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>76</v>
       </c>
       <c r="E79" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F79" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2386,16 +2407,16 @@
         <v>-5</v>
       </c>
       <c r="D80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>71</v>
       </c>
       <c r="E80" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F80" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2409,16 +2430,16 @@
         <v>-190</v>
       </c>
       <c r="D81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>241</v>
       </c>
       <c r="E81" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F81" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2432,16 +2453,16 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>242</v>
       </c>
       <c r="E82" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F82" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2455,16 +2476,16 @@
         <v>11</v>
       </c>
       <c r="D83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>253</v>
       </c>
       <c r="E83" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F83" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2478,16 +2499,16 @@
         <v>-18</v>
       </c>
       <c r="D84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>235</v>
       </c>
       <c r="E84" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F84" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2501,16 +2522,16 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>235</v>
       </c>
       <c r="E85" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F85" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2524,16 +2545,16 @@
         <v>-11</v>
       </c>
       <c r="D86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>224</v>
       </c>
       <c r="E86" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F86" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2547,16 +2568,16 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>225</v>
       </c>
       <c r="E87" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F87" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2570,16 +2591,16 @@
         <v>14</v>
       </c>
       <c r="D88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>239</v>
       </c>
       <c r="E88" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F88" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -2593,16 +2614,16 @@
         <v>19</v>
       </c>
       <c r="D89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>258</v>
       </c>
       <c r="E89" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F89" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -2616,16 +2637,16 @@
         <v>12</v>
       </c>
       <c r="D90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="E90" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F90" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -2639,16 +2660,16 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="E91" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F91" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -2662,16 +2683,16 @@
         <v>18</v>
       </c>
       <c r="D92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>288</v>
       </c>
       <c r="E92" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F92" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -2685,16 +2706,16 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>288</v>
       </c>
       <c r="E93" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F93" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -2708,16 +2729,16 @@
         <v>19</v>
       </c>
       <c r="D94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>307</v>
       </c>
       <c r="E94" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F94" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2731,16 +2752,16 @@
         <v>10</v>
       </c>
       <c r="D95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>317</v>
       </c>
       <c r="E95" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F95" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -2754,16 +2775,16 @@
         <v>13</v>
       </c>
       <c r="D96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>330</v>
       </c>
       <c r="E96" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F96" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -2777,16 +2798,16 @@
         <v>10</v>
       </c>
       <c r="D97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="E97" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F97" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,16 +2821,16 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>340</v>
       </c>
       <c r="E98" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F98" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,16 +2844,16 @@
         <v>19</v>
       </c>
       <c r="D99">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>359</v>
       </c>
       <c r="E99" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F99" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,16 +2867,16 @@
         <v>11</v>
       </c>
       <c r="D100">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="E100" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F100" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -2869,16 +2890,16 @@
         <v>20</v>
       </c>
       <c r="D101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="E101" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F101" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -2892,16 +2913,16 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>30</v>
       </c>
       <c r="E102" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F102" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -2915,16 +2936,16 @@
         <v>10</v>
       </c>
       <c r="D103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="E103" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>É</v>
       </c>
       <c r="F103" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -2938,16 +2959,16 @@
         <v>8</v>
       </c>
       <c r="D104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="E104" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F104" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -2961,16 +2982,16 @@
         <v>6</v>
       </c>
       <c r="D105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="E105" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F105" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -2984,16 +3005,16 @@
         <v>-3</v>
       </c>
       <c r="D106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>51</v>
       </c>
       <c r="E106" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F106" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3007,16 +3028,16 @@
         <v>-3</v>
       </c>
       <c r="D107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>48</v>
       </c>
       <c r="E107" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F107" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3030,16 +3051,16 @@
         <v>6</v>
       </c>
       <c r="D108">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="E108" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F108" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3053,16 +3074,16 @@
         <v>13</v>
       </c>
       <c r="D109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>67</v>
       </c>
       <c r="E109" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F109" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3076,16 +3097,16 @@
         <v>10</v>
       </c>
       <c r="D110">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>77</v>
       </c>
       <c r="E110" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F110" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3099,16 +3120,16 @@
         <v>11</v>
       </c>
       <c r="D111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>88</v>
       </c>
       <c r="E111" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F111" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3122,16 +3143,16 @@
         <v>14</v>
       </c>
       <c r="D112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>102</v>
       </c>
       <c r="E112" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F112" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3145,16 +3166,16 @@
         <v>11</v>
       </c>
       <c r="D113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>113</v>
       </c>
       <c r="E113" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3168,16 +3189,16 @@
         <v>-3</v>
       </c>
       <c r="D114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>110</v>
       </c>
       <c r="E114" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F114" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3191,16 +3212,16 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>111</v>
       </c>
       <c r="E115" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3214,16 +3235,16 @@
         <v>18</v>
       </c>
       <c r="D116">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>129</v>
       </c>
       <c r="E116" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3237,16 +3258,16 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>130</v>
       </c>
       <c r="E117" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>K</v>
       </c>
       <c r="F117" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,16 +3281,16 @@
         <v>9</v>
       </c>
       <c r="D118">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>139</v>
       </c>
       <c r="E118" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F118" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,16 +3304,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>156</v>
       </c>
       <c r="E119" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F119" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3306,16 +3327,16 @@
         <v>8</v>
       </c>
       <c r="D120">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>164</v>
       </c>
       <c r="E120" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F120" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3329,16 +3350,16 @@
         <v>18</v>
       </c>
       <c r="D121">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>182</v>
       </c>
       <c r="E121" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F121" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3352,16 +3373,16 @@
         <v>18</v>
       </c>
       <c r="D122">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="E122" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F122" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3375,16 +3396,16 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>200</v>
       </c>
       <c r="E123" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F123" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,16 +3419,16 @@
         <v>4</v>
       </c>
       <c r="D124">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>204</v>
       </c>
       <c r="E124" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F124" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3421,16 +3442,16 @@
         <v>15</v>
       </c>
       <c r="D125">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>219</v>
       </c>
       <c r="E125" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F125" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3444,16 +3465,16 @@
         <v>5</v>
       </c>
       <c r="D126">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>224</v>
       </c>
       <c r="E126" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
       <c r="F126" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -3467,16 +3488,16 @@
         <v>20</v>
       </c>
       <c r="D127">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>244</v>
       </c>
       <c r="E127" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F127" t="str">
-        <f t="shared" si="6"/>
-        <v>Igaz</v>
+        <f t="shared" si="5"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -3490,16 +3511,16 @@
         <v>13</v>
       </c>
       <c r="D128">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>257</v>
       </c>
       <c r="E128" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F128" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -3513,16 +3534,16 @@
         <v>10</v>
       </c>
       <c r="D129">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>267</v>
       </c>
       <c r="E129" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F129" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -3536,16 +3557,16 @@
         <v>9</v>
       </c>
       <c r="D130">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>276</v>
       </c>
       <c r="E130" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>Ny</v>
       </c>
       <c r="F130" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -3559,16 +3580,16 @@
         <v>18</v>
       </c>
       <c r="D131">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>294</v>
       </c>
       <c r="E131" t="str">
-        <f t="shared" ref="E131:E194" si="7">IF(OR(D131&gt;=315,D131&lt;45),"É",IF(AND(D131&gt;=45,D131&lt;135),"K",IF(AND(D131&gt;=135,D131&lt;225),"D","Ny")))</f>
+        <f t="shared" ref="E131:E194" si="6">IF(AND(D131&gt;=45,D131&lt;135),"K",IF(AND(D131&gt;=135,D131&lt;225),"D",IF(AND(D131&gt;=225,D131&lt;315),"Ny","É")))</f>
         <v>Ny</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="6"/>
-        <v>Hamis</v>
+        <f t="shared" si="5"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -3582,16 +3603,16 @@
         <v>12</v>
       </c>
       <c r="D132">
-        <f t="shared" ref="D132:D195" si="8">MOD(D131+C132,360)</f>
+        <f t="shared" ref="D132:D195" si="7">MOD(D131+C132,360)</f>
         <v>306</v>
       </c>
       <c r="E132" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F132" t="str">
-        <f t="shared" ref="F132:F195" si="9">IF(E132=E131,"Hamis","Igaz")</f>
-        <v>Hamis</v>
+        <f t="shared" ref="F132:F195" si="8">IF(E132=E131,"HAMIS","IGAZ")</f>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -3605,16 +3626,16 @@
         <v>9</v>
       </c>
       <c r="D133">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>315</v>
       </c>
       <c r="E133" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F133" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -3628,16 +3649,16 @@
         <v>12</v>
       </c>
       <c r="D134">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>327</v>
       </c>
       <c r="E134" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F134" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -3651,16 +3672,16 @@
         <v>20</v>
       </c>
       <c r="D135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>347</v>
       </c>
       <c r="E135" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F135" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,16 +3695,16 @@
         <v>3</v>
       </c>
       <c r="D136">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>350</v>
       </c>
       <c r="E136" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F136" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -3697,16 +3718,16 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>357</v>
       </c>
       <c r="E137" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -3720,16 +3741,16 @@
         <v>16</v>
       </c>
       <c r="D138">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="E138" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F138" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -3743,16 +3764,16 @@
         <v>16</v>
       </c>
       <c r="D139">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>29</v>
       </c>
       <c r="E139" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F139" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -3766,16 +3787,16 @@
         <v>14</v>
       </c>
       <c r="D140">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>43</v>
       </c>
       <c r="E140" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F140" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -3789,16 +3810,16 @@
         <v>3</v>
       </c>
       <c r="D141">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>46</v>
       </c>
       <c r="E141" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F141" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -3812,16 +3833,16 @@
         <v>6</v>
       </c>
       <c r="D142">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>52</v>
       </c>
       <c r="E142" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F142" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -3835,16 +3856,16 @@
         <v>2</v>
       </c>
       <c r="D143">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>54</v>
       </c>
       <c r="E143" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F143" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -3858,16 +3879,16 @@
         <v>10</v>
       </c>
       <c r="D144">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>64</v>
       </c>
       <c r="E144" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F144" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -3881,16 +3902,16 @@
         <v>12</v>
       </c>
       <c r="D145">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>76</v>
       </c>
       <c r="E145" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F145" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -3904,16 +3925,16 @@
         <v>7</v>
       </c>
       <c r="D146">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>83</v>
       </c>
       <c r="E146" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F146" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -3927,16 +3948,16 @@
         <v>15</v>
       </c>
       <c r="D147">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>98</v>
       </c>
       <c r="E147" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F147" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,16 +3971,16 @@
         <v>-3</v>
       </c>
       <c r="D148">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>95</v>
       </c>
       <c r="E148" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F148" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -3973,16 +3994,16 @@
         <v>10</v>
       </c>
       <c r="D149">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>105</v>
       </c>
       <c r="E149" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F149" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -3996,16 +4017,16 @@
         <v>10</v>
       </c>
       <c r="D150">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>115</v>
       </c>
       <c r="E150" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F150" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -4019,16 +4040,16 @@
         <v>-2</v>
       </c>
       <c r="D151">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>113</v>
       </c>
       <c r="E151" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F151" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4042,16 +4063,16 @@
         <v>2</v>
       </c>
       <c r="D152">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>115</v>
       </c>
       <c r="E152" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F152" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4065,16 +4086,16 @@
         <v>-3</v>
       </c>
       <c r="D153">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>112</v>
       </c>
       <c r="E153" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F153" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4088,16 +4109,16 @@
         <v>4</v>
       </c>
       <c r="D154">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>116</v>
       </c>
       <c r="E154" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F154" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4111,16 +4132,16 @@
         <v>9</v>
       </c>
       <c r="D155">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>125</v>
       </c>
       <c r="E155" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F155" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4134,16 +4155,16 @@
         <v>9</v>
       </c>
       <c r="D156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>134</v>
       </c>
       <c r="E156" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F156" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4157,16 +4178,16 @@
         <v>4</v>
       </c>
       <c r="D157">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>138</v>
       </c>
       <c r="E157" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4180,16 +4201,16 @@
         <v>17</v>
       </c>
       <c r="D158">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>155</v>
       </c>
       <c r="E158" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4203,16 +4224,16 @@
         <v>12</v>
       </c>
       <c r="D159">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>167</v>
       </c>
       <c r="E159" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F159" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4226,16 +4247,16 @@
         <v>-1</v>
       </c>
       <c r="D160">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>166</v>
       </c>
       <c r="E160" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4249,16 +4270,16 @@
         <v>7</v>
       </c>
       <c r="D161">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>173</v>
       </c>
       <c r="E161" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4272,16 +4293,16 @@
         <v>17</v>
       </c>
       <c r="D162">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>190</v>
       </c>
       <c r="E162" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4295,16 +4316,16 @@
         <v>18</v>
       </c>
       <c r="D163">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>208</v>
       </c>
       <c r="E163" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F163" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4318,16 +4339,16 @@
         <v>4</v>
       </c>
       <c r="D164">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>212</v>
       </c>
       <c r="E164" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F164" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4341,16 +4362,16 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>212</v>
       </c>
       <c r="E165" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>D</v>
       </c>
       <c r="F165" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4364,16 +4385,16 @@
         <v>17</v>
       </c>
       <c r="D166">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>229</v>
       </c>
       <c r="E166" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F166" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4387,16 +4408,16 @@
         <v>18</v>
       </c>
       <c r="D167">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>247</v>
       </c>
       <c r="E167" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F167" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4410,16 +4431,16 @@
         <v>10</v>
       </c>
       <c r="D168">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>257</v>
       </c>
       <c r="E168" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F168" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4433,16 +4454,16 @@
         <v>10</v>
       </c>
       <c r="D169">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>267</v>
       </c>
       <c r="E169" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F169" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -4456,16 +4477,16 @@
         <v>17</v>
       </c>
       <c r="D170">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>284</v>
       </c>
       <c r="E170" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F170" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,16 +4500,16 @@
         <v>3</v>
       </c>
       <c r="D171">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>287</v>
       </c>
       <c r="E171" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F171" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -4502,16 +4523,16 @@
         <v>20</v>
       </c>
       <c r="D172">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>307</v>
       </c>
       <c r="E172" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F172" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -4525,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="D173">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>308</v>
       </c>
       <c r="E173" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F173" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -4548,16 +4569,16 @@
         <v>3</v>
       </c>
       <c r="D174">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>311</v>
       </c>
       <c r="E174" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F174" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -4571,16 +4592,16 @@
         <v>5</v>
       </c>
       <c r="D175">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>316</v>
       </c>
       <c r="E175" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F175" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -4594,16 +4615,16 @@
         <v>-4</v>
       </c>
       <c r="D176">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>312</v>
       </c>
       <c r="E176" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F176" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -4617,16 +4638,16 @@
         <v>-3</v>
       </c>
       <c r="D177">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>309</v>
       </c>
       <c r="E177" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F177" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -4640,16 +4661,16 @@
         <v>4</v>
       </c>
       <c r="D178">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>313</v>
       </c>
       <c r="E178" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Ny</v>
       </c>
       <c r="F178" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -4663,16 +4684,16 @@
         <v>4</v>
       </c>
       <c r="D179">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>317</v>
       </c>
       <c r="E179" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F179" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -4686,16 +4707,16 @@
         <v>10</v>
       </c>
       <c r="D180">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>327</v>
       </c>
       <c r="E180" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F180" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -4709,16 +4730,16 @@
         <v>2</v>
       </c>
       <c r="D181">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>329</v>
       </c>
       <c r="E181" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F181" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -4732,16 +4753,16 @@
         <v>20</v>
       </c>
       <c r="D182">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>349</v>
       </c>
       <c r="E182" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F182" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -4755,16 +4776,16 @@
         <v>18</v>
       </c>
       <c r="D183">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="E183" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F183" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -4778,16 +4799,16 @@
         <v>-1</v>
       </c>
       <c r="D184">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="E184" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F184" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -4801,16 +4822,16 @@
         <v>-5</v>
       </c>
       <c r="D185">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E185" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F185" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -4824,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E186" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F186" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -4847,16 +4868,16 @@
         <v>-5</v>
       </c>
       <c r="D187">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>356</v>
       </c>
       <c r="E187" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F187" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -4870,16 +4891,16 @@
         <v>10</v>
       </c>
       <c r="D188">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="E188" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F188" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -4893,16 +4914,16 @@
         <v>9</v>
       </c>
       <c r="D189">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="E189" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F189" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -4916,16 +4937,16 @@
         <v>11</v>
       </c>
       <c r="D190">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>26</v>
       </c>
       <c r="E190" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F190" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,16 +4960,16 @@
         <v>15</v>
       </c>
       <c r="D191">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>41</v>
       </c>
       <c r="E191" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>É</v>
       </c>
       <c r="F191" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -4962,16 +4983,16 @@
         <v>18</v>
       </c>
       <c r="D192">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>59</v>
       </c>
       <c r="E192" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F192" t="str">
-        <f t="shared" si="9"/>
-        <v>Igaz</v>
+        <f t="shared" si="8"/>
+        <v>IGAZ</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -4985,16 +5006,16 @@
         <v>-1</v>
       </c>
       <c r="D193">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>58</v>
       </c>
       <c r="E193" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F193" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
@@ -5008,16 +5029,16 @@
         <v>17</v>
       </c>
       <c r="D194">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>75</v>
       </c>
       <c r="E194" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>K</v>
       </c>
       <c r="F194" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5031,16 +5052,16 @@
         <v>2</v>
       </c>
       <c r="D195">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>77</v>
       </c>
       <c r="E195" t="str">
-        <f t="shared" ref="E195:E201" si="10">IF(OR(D195&gt;=315,D195&lt;45),"É",IF(AND(D195&gt;=45,D195&lt;135),"K",IF(AND(D195&gt;=135,D195&lt;225),"D","Ny")))</f>
+        <f t="shared" ref="E195:E201" si="9">IF(AND(D195&gt;=45,D195&lt;135),"K",IF(AND(D195&gt;=135,D195&lt;225),"D",IF(AND(D195&gt;=225,D195&lt;315),"Ny","É")))</f>
         <v>K</v>
       </c>
       <c r="F195" t="str">
-        <f t="shared" si="9"/>
-        <v>Hamis</v>
+        <f t="shared" si="8"/>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
@@ -5054,16 +5075,16 @@
         <v>-4</v>
       </c>
       <c r="D196">
-        <f t="shared" ref="D196:D201" si="11">MOD(D195+C196,360)</f>
+        <f t="shared" ref="D196:D201" si="10">MOD(D195+C196,360)</f>
         <v>73</v>
       </c>
       <c r="E196" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>K</v>
       </c>
       <c r="F196" t="str">
-        <f t="shared" ref="F196:F201" si="12">IF(E196=E195,"Hamis","Igaz")</f>
-        <v>Hamis</v>
+        <f t="shared" ref="F196:F201" si="11">IF(E196=E195,"HAMIS","IGAZ")</f>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5077,16 +5098,16 @@
         <v>1</v>
       </c>
       <c r="D197">
+        <f t="shared" si="10"/>
+        <v>74</v>
+      </c>
+      <c r="E197" t="str">
+        <f t="shared" si="9"/>
+        <v>K</v>
+      </c>
+      <c r="F197" t="str">
         <f t="shared" si="11"/>
-        <v>74</v>
-      </c>
-      <c r="E197" t="str">
-        <f t="shared" si="10"/>
-        <v>K</v>
-      </c>
-      <c r="F197" t="str">
-        <f t="shared" si="12"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5100,16 +5121,16 @@
         <v>19</v>
       </c>
       <c r="D198">
+        <f t="shared" si="10"/>
+        <v>93</v>
+      </c>
+      <c r="E198" t="str">
+        <f t="shared" si="9"/>
+        <v>K</v>
+      </c>
+      <c r="F198" t="str">
         <f t="shared" si="11"/>
-        <v>93</v>
-      </c>
-      <c r="E198" t="str">
-        <f t="shared" si="10"/>
-        <v>K</v>
-      </c>
-      <c r="F198" t="str">
-        <f t="shared" si="12"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5123,16 +5144,16 @@
         <v>9</v>
       </c>
       <c r="D199">
+        <f t="shared" si="10"/>
+        <v>102</v>
+      </c>
+      <c r="E199" t="str">
+        <f t="shared" si="9"/>
+        <v>K</v>
+      </c>
+      <c r="F199" t="str">
         <f t="shared" si="11"/>
-        <v>102</v>
-      </c>
-      <c r="E199" t="str">
-        <f t="shared" si="10"/>
-        <v>K</v>
-      </c>
-      <c r="F199" t="str">
-        <f t="shared" si="12"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -5146,16 +5167,16 @@
         <v>7</v>
       </c>
       <c r="D200">
+        <f t="shared" si="10"/>
+        <v>109</v>
+      </c>
+      <c r="E200" t="str">
+        <f t="shared" si="9"/>
+        <v>K</v>
+      </c>
+      <c r="F200" t="str">
         <f t="shared" si="11"/>
-        <v>109</v>
-      </c>
-      <c r="E200" t="str">
-        <f t="shared" si="10"/>
-        <v>K</v>
-      </c>
-      <c r="F200" t="str">
-        <f t="shared" si="12"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -5169,19 +5190,20 @@
         <v>3</v>
       </c>
       <c r="D201">
+        <f t="shared" si="10"/>
+        <v>112</v>
+      </c>
+      <c r="E201" t="str">
+        <f t="shared" si="9"/>
+        <v>K</v>
+      </c>
+      <c r="F201" t="str">
         <f t="shared" si="11"/>
-        <v>112</v>
-      </c>
-      <c r="E201" t="str">
-        <f t="shared" si="10"/>
-        <v>K</v>
-      </c>
-      <c r="F201" t="str">
-        <f t="shared" si="12"/>
-        <v>Hamis</v>
+        <v>HAMIS</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>